--- a/Base_de_donnees/Fichiers_metadonnees/videInstr.xlsx
+++ b/Base_de_donnees/Fichiers_metadonnees/videInstr.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instruments" sheetId="1" state="visible" r:id="rId3"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
   <si>
     <t xml:space="preserve">numéro_serie</t>
   </si>
@@ -54,6 +54,9 @@
   </si>
   <si>
     <t xml:space="preserve">description (unique)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">num_colonne</t>
   </si>
   <si>
     <t xml:space="preserve">id_initial</t>
@@ -98,7 +101,7 @@
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yy"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -134,6 +137,12 @@
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="0"/>
     </font>
     <font>
       <sz val="12"/>
@@ -185,7 +194,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -202,7 +211,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -405,11 +418,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I39"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.52"/>
@@ -571,20 +583,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E39"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="25.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="33.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="85.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="25.04"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="21.38"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>7</v>
       </c>
@@ -594,160 +605,162 @@
       <c r="C1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="2"/>
+      <c r="D1" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="E1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="4"/>
-      <c r="C2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="6"/>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="4"/>
-      <c r="C3" s="5"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="4"/>
-      <c r="C4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="4"/>
-      <c r="C5" s="5"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="6"/>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="4"/>
-      <c r="C6" s="5"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="6"/>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="4"/>
-      <c r="C7" s="5"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="6"/>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="4"/>
-      <c r="C8" s="5"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="6"/>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="4"/>
-      <c r="C9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="6"/>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="4"/>
-      <c r="C10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="6"/>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="4"/>
-      <c r="C11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="6"/>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="4"/>
-      <c r="C12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="6"/>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="4"/>
-      <c r="C13" s="5"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="6"/>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="4"/>
-      <c r="C14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="6"/>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="4"/>
-      <c r="C15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="6"/>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="4"/>
-      <c r="C16" s="5"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="6"/>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="4"/>
-      <c r="C17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="6"/>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="4"/>
-      <c r="C18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="6"/>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="4"/>
-      <c r="C19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="6"/>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="4"/>
-      <c r="C20" s="5"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="6"/>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="4"/>
-      <c r="C21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="6"/>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="4"/>
-      <c r="C22" s="5"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="6"/>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="4"/>
-      <c r="C23" s="5"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="6"/>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="4"/>
-      <c r="C24" s="5"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="6"/>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="4"/>
-      <c r="C25" s="5"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="6"/>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="4"/>
-      <c r="C26" s="5"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="6"/>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="4"/>
-      <c r="C27" s="5"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="6"/>
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="4"/>
-      <c r="C28" s="5"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="6"/>
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="4"/>
-      <c r="C29" s="5"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="6"/>
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="4"/>
-      <c r="C30" s="5"/>
+      <c r="B30" s="5"/>
+      <c r="C30" s="6"/>
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="4"/>
-      <c r="C31" s="5"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="6"/>
     </row>
     <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="4"/>
-      <c r="C32" s="5"/>
+      <c r="B32" s="5"/>
+      <c r="C32" s="6"/>
     </row>
     <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="4"/>
-      <c r="C33" s="5"/>
+      <c r="B33" s="5"/>
+      <c r="C33" s="6"/>
     </row>
     <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="4"/>
-      <c r="C34" s="5"/>
+      <c r="B34" s="5"/>
+      <c r="C34" s="6"/>
     </row>
     <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="4"/>
-      <c r="C35" s="5"/>
+      <c r="B35" s="5"/>
+      <c r="C35" s="6"/>
     </row>
     <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="4"/>
-      <c r="C36" s="5"/>
+      <c r="B36" s="5"/>
+      <c r="C36" s="6"/>
     </row>
     <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="4"/>
-      <c r="C37" s="5"/>
+      <c r="B37" s="5"/>
+      <c r="C37" s="6"/>
     </row>
     <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="4"/>
-      <c r="C38" s="5"/>
+      <c r="B38" s="5"/>
+      <c r="C38" s="6"/>
     </row>
     <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="4"/>
-      <c r="C39" s="5"/>
+      <c r="B39" s="5"/>
+      <c r="C39" s="6"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -763,11 +776,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="37"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="35.48"/>
@@ -778,24 +790,24 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -811,11 +823,10 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24.62"/>
@@ -825,22 +836,22 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="6"/>
-      <c r="C2" s="5"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="6"/>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="6"/>
-      <c r="C3" s="5"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="6"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -856,11 +867,10 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D39"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="34.51"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="35.75"/>
@@ -868,207 +878,207 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6"/>
-      <c r="B2" s="7"/>
-      <c r="D2" s="5"/>
+      <c r="A2" s="7"/>
+      <c r="B2" s="8"/>
+      <c r="D2" s="6"/>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6"/>
-      <c r="B3" s="7"/>
-      <c r="D3" s="5"/>
+      <c r="A3" s="7"/>
+      <c r="B3" s="8"/>
+      <c r="D3" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6"/>
-      <c r="B4" s="7"/>
-      <c r="D4" s="5"/>
+      <c r="A4" s="7"/>
+      <c r="B4" s="8"/>
+      <c r="D4" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6"/>
-      <c r="B5" s="7"/>
-      <c r="D5" s="5"/>
+      <c r="A5" s="7"/>
+      <c r="B5" s="8"/>
+      <c r="D5" s="6"/>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6"/>
-      <c r="B6" s="7"/>
-      <c r="D6" s="5"/>
+      <c r="A6" s="7"/>
+      <c r="B6" s="8"/>
+      <c r="D6" s="6"/>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6"/>
-      <c r="B7" s="7"/>
-      <c r="D7" s="5"/>
+      <c r="A7" s="7"/>
+      <c r="B7" s="8"/>
+      <c r="D7" s="6"/>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6"/>
-      <c r="B8" s="7"/>
-      <c r="D8" s="5"/>
+      <c r="A8" s="7"/>
+      <c r="B8" s="8"/>
+      <c r="D8" s="6"/>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6"/>
-      <c r="B9" s="7"/>
-      <c r="D9" s="5"/>
+      <c r="A9" s="7"/>
+      <c r="B9" s="8"/>
+      <c r="D9" s="6"/>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6"/>
-      <c r="B10" s="7"/>
-      <c r="D10" s="5"/>
+      <c r="A10" s="7"/>
+      <c r="B10" s="8"/>
+      <c r="D10" s="6"/>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6"/>
-      <c r="B11" s="7"/>
-      <c r="D11" s="5"/>
+      <c r="A11" s="7"/>
+      <c r="B11" s="8"/>
+      <c r="D11" s="6"/>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6"/>
-      <c r="B12" s="7"/>
-      <c r="D12" s="5"/>
+      <c r="A12" s="7"/>
+      <c r="B12" s="8"/>
+      <c r="D12" s="6"/>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6"/>
-      <c r="B13" s="7"/>
-      <c r="D13" s="5"/>
+      <c r="A13" s="7"/>
+      <c r="B13" s="8"/>
+      <c r="D13" s="6"/>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6"/>
-      <c r="B14" s="7"/>
-      <c r="D14" s="5"/>
+      <c r="A14" s="7"/>
+      <c r="B14" s="8"/>
+      <c r="D14" s="6"/>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6"/>
-      <c r="B15" s="7"/>
-      <c r="D15" s="5"/>
+      <c r="A15" s="7"/>
+      <c r="B15" s="8"/>
+      <c r="D15" s="6"/>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6"/>
-      <c r="B16" s="7"/>
-      <c r="D16" s="5"/>
+      <c r="A16" s="7"/>
+      <c r="B16" s="8"/>
+      <c r="D16" s="6"/>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6"/>
-      <c r="B17" s="7"/>
-      <c r="D17" s="5"/>
+      <c r="A17" s="7"/>
+      <c r="B17" s="8"/>
+      <c r="D17" s="6"/>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6"/>
-      <c r="B18" s="7"/>
-      <c r="D18" s="5"/>
+      <c r="A18" s="7"/>
+      <c r="B18" s="8"/>
+      <c r="D18" s="6"/>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6"/>
-      <c r="B19" s="7"/>
-      <c r="D19" s="5"/>
+      <c r="A19" s="7"/>
+      <c r="B19" s="8"/>
+      <c r="D19" s="6"/>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6"/>
-      <c r="B20" s="7"/>
-      <c r="D20" s="5"/>
+      <c r="A20" s="7"/>
+      <c r="B20" s="8"/>
+      <c r="D20" s="6"/>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6"/>
-      <c r="B21" s="7"/>
-      <c r="D21" s="5"/>
+      <c r="A21" s="7"/>
+      <c r="B21" s="8"/>
+      <c r="D21" s="6"/>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6"/>
-      <c r="B22" s="7"/>
-      <c r="D22" s="5"/>
+      <c r="A22" s="7"/>
+      <c r="B22" s="8"/>
+      <c r="D22" s="6"/>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="6"/>
-      <c r="B23" s="7"/>
-      <c r="D23" s="5"/>
+      <c r="A23" s="7"/>
+      <c r="B23" s="8"/>
+      <c r="D23" s="6"/>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6"/>
-      <c r="B24" s="7"/>
-      <c r="D24" s="5"/>
+      <c r="A24" s="7"/>
+      <c r="B24" s="8"/>
+      <c r="D24" s="6"/>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6"/>
-      <c r="B25" s="7"/>
-      <c r="D25" s="5"/>
+      <c r="A25" s="7"/>
+      <c r="B25" s="8"/>
+      <c r="D25" s="6"/>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6"/>
-      <c r="B26" s="7"/>
-      <c r="D26" s="5"/>
+      <c r="A26" s="7"/>
+      <c r="B26" s="8"/>
+      <c r="D26" s="6"/>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6"/>
-      <c r="B27" s="7"/>
-      <c r="D27" s="5"/>
+      <c r="A27" s="7"/>
+      <c r="B27" s="8"/>
+      <c r="D27" s="6"/>
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6"/>
-      <c r="B28" s="7"/>
-      <c r="D28" s="5"/>
+      <c r="A28" s="7"/>
+      <c r="B28" s="8"/>
+      <c r="D28" s="6"/>
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="6"/>
-      <c r="B29" s="7"/>
-      <c r="D29" s="5"/>
+      <c r="A29" s="7"/>
+      <c r="B29" s="8"/>
+      <c r="D29" s="6"/>
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="6"/>
-      <c r="B30" s="7"/>
-      <c r="D30" s="5"/>
+      <c r="A30" s="7"/>
+      <c r="B30" s="8"/>
+      <c r="D30" s="6"/>
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="6"/>
-      <c r="B31" s="7"/>
-      <c r="D31" s="5"/>
+      <c r="A31" s="7"/>
+      <c r="B31" s="8"/>
+      <c r="D31" s="6"/>
     </row>
     <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6"/>
-      <c r="B32" s="7"/>
-      <c r="D32" s="5"/>
+      <c r="A32" s="7"/>
+      <c r="B32" s="8"/>
+      <c r="D32" s="6"/>
     </row>
     <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6"/>
-      <c r="B33" s="7"/>
-      <c r="D33" s="5"/>
+      <c r="A33" s="7"/>
+      <c r="B33" s="8"/>
+      <c r="D33" s="6"/>
     </row>
     <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="6"/>
-      <c r="B34" s="7"/>
-      <c r="D34" s="5"/>
+      <c r="A34" s="7"/>
+      <c r="B34" s="8"/>
+      <c r="D34" s="6"/>
     </row>
     <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="6"/>
-      <c r="B35" s="7"/>
-      <c r="D35" s="5"/>
+      <c r="A35" s="7"/>
+      <c r="B35" s="8"/>
+      <c r="D35" s="6"/>
     </row>
     <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="6"/>
-      <c r="B36" s="7"/>
-      <c r="D36" s="5"/>
+      <c r="A36" s="7"/>
+      <c r="B36" s="8"/>
+      <c r="D36" s="6"/>
     </row>
     <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="6"/>
-      <c r="B37" s="7"/>
-      <c r="D37" s="5"/>
+      <c r="A37" s="7"/>
+      <c r="B37" s="8"/>
+      <c r="D37" s="6"/>
     </row>
     <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="6"/>
-      <c r="B38" s="7"/>
-      <c r="D38" s="5"/>
+      <c r="A38" s="7"/>
+      <c r="B38" s="8"/>
+      <c r="D38" s="6"/>
     </row>
     <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="6"/>
-      <c r="B39" s="7"/>
-      <c r="D39" s="5"/>
+      <c r="A39" s="7"/>
+      <c r="B39" s="8"/>
+      <c r="D39" s="6"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
